--- a/OCH_Plan_Library_Template_1.xlsx
+++ b/OCH_Plan_Library_Template_1.xlsx
@@ -3748,7 +3748,11 @@
           <t>34'-10"</t>
         </is>
       </c>
-      <c r="F45" s="48" t="n"/>
+      <c r="F45" s="48" t="inlineStr">
+        <is>
+          <t>76'-6"</t>
+        </is>
+      </c>
       <c r="G45" s="48" t="n"/>
       <c r="H45" s="49" t="n">
         <v>2631</v>
@@ -3776,9 +3780,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P45" s="47" t="inlineStr">
-        <is>
-          <t>WIDTH confirmed 34'-10" (repeats twice in CAD text). DEPTH UNCONFIRMED — the extraction shows both 76'-6" and 76'-0" once each (neither repeats, so the repeat-value check fails). Prior library note said min 76'-6"/max 77'-6"; CAD does not clearly confirm either. Do not treat F45 as reliable until re-verified against the rasterized plan sheet. AC sqft is elevation-specific: A=2631, B=2631, C=2601 (prior library had flat 2601 for all three).</t>
+      <c r="P45" s="71" t="inlineStr">
+        <is>
+          <t>WIDTH confirmed 34'-10" (repeats twice in CAD text). DEPTH UNCONFIRMED — the extraction shows both 76'-6" and 76'-0" once each (neither repeats, so the repeat-value check fails). Prior library note said min 76'-6"/max 77'-6"; CAD does not clearly confirm either. Do not treat F45 as reliable until re-verified against the rasterized plan sheet. AC sqft is elevation-specific: A=2631, B=2631, C=2601 (prior library had flat 2601 for all three).  Depth 76'-6" measured 9/14/26 from Holland J35A (7-20-26). Elev A carries two competing chains, 76'-6" and 76'-0"; took the larger as finish face per the masonry-vs-frame convention (plan carries both MASONRY FOOTAGES and EXTERIOR OF FRAME tables). Slightly less certain than B/C, which each repeat cleanly.</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3810,11 @@
           <t>34'-10"</t>
         </is>
       </c>
-      <c r="F46" s="48" t="n"/>
+      <c r="F46" s="48" t="inlineStr">
+        <is>
+          <t>77'-6"</t>
+        </is>
+      </c>
       <c r="G46" s="48" t="n"/>
       <c r="H46" s="49" t="n">
         <v>2631</v>
@@ -3834,9 +3842,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P46" s="47" t="inlineStr">
-        <is>
-          <t>Same width/depth-uncertainty as A. AC sqft 2631 (elevation-specific, was flat 2601).</t>
+      <c r="P46" s="71" t="inlineStr">
+        <is>
+          <t>Same width/depth-uncertainty as A. AC sqft 2631 (elevation-specific, was flat 2601).  Depth 77'-6" measured 9/14/26 — repeats twice non-adjacently, clean confirmation. DEEPER THAN A/C by 1'-0".</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3872,11 @@
           <t>34'-10"</t>
         </is>
       </c>
-      <c r="F47" s="48" t="n"/>
+      <c r="F47" s="48" t="inlineStr">
+        <is>
+          <t>76'-6"</t>
+        </is>
+      </c>
       <c r="G47" s="48" t="n"/>
       <c r="H47" s="49" t="n">
         <v>2601</v>
@@ -3892,9 +3904,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P47" s="47" t="inlineStr">
-        <is>
-          <t>Same width as A. AC sqft 2601 (matches prior flat value for this elevation only).</t>
+      <c r="P47" s="71" t="inlineStr">
+        <is>
+          <t>Same width as A. AC sqft 2601 (matches prior flat value for this elevation only).  Depth 76'-6" measured 9/14/26 — repeats twice non-adjacently, clean confirmation.</t>
         </is>
       </c>
     </row>
@@ -4103,8 +4115,16 @@
       <c r="D51" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
+      <c r="E51" s="48" t="inlineStr">
+        <is>
+          <t>34'-10"</t>
+        </is>
+      </c>
+      <c r="F51" s="48" t="inlineStr">
+        <is>
+          <t>83'-0"</t>
+        </is>
+      </c>
       <c r="G51" s="48" t="n"/>
       <c r="H51" s="47" t="n">
         <v>1933</v>
@@ -4126,9 +4146,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P51" s="47" t="inlineStr">
-        <is>
-          <t>UNCHANGED — the Parker PDF you sent contained only repeated title-block/footer text (plan number, address, copyright line) with no floor plan, dimension, or area-table content extracted. Existing library values (AC 1933, 1-story) are retained as-is; width/depth are still unconfirmed. Please resend the Parker plan PDF — it looks like the file didn't include the actual drawing pages.</t>
+      <c r="P51" s="71" t="inlineStr">
+        <is>
+          <t>UNCHANGED — the Parker PDF you sent contained only repeated title-block/footer text (plan number, address, copyright line) with no floor plan, dimension, or area-table content extracted. Existing library values (AC 1933, 1-story) are retained as-is; width/depth are still unconfirmed. Please resend the Parker plan PDF — it looks like the file didn't include the actual drawing pages.  WIDTH 34'-10" confirmed 9/14/26 (sub-chain 10'-11"+4'-0"+19'-11"=34'-10").  DEPTH RESOLVED 9/15/26 = 83'-0". Plan shows two chains 83'-0" and 88'-0" (5'-0" apart, ~2.5 ft at each end = roof overhang). Settled empirically: Parker is built on N-13, N-4 and P-17, all 110 ft deep. At 83'-0" all three clear by ~2 ft; at 88'-0" all three would have been impossible to build. 83'-0" is the body-plus-porch dimension, consistent with the other Heights plans.</t>
         </is>
       </c>
     </row>
@@ -4151,8 +4171,16 @@
       <c r="D52" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="E52" s="48" t="n"/>
-      <c r="F52" s="48" t="n"/>
+      <c r="E52" s="48" t="inlineStr">
+        <is>
+          <t>34'-10"</t>
+        </is>
+      </c>
+      <c r="F52" s="48" t="inlineStr">
+        <is>
+          <t>83'-0"</t>
+        </is>
+      </c>
       <c r="G52" s="48" t="n"/>
       <c r="H52" s="47" t="n">
         <v>1933</v>
@@ -4174,9 +4202,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P52" s="47" t="inlineStr">
-        <is>
-          <t>See note on row 51 — Parker PDF had no usable content.</t>
+      <c r="P52" s="71" t="inlineStr">
+        <is>
+          <t>See note on row 51 — Parker PDF had no usable content.  DEPTH RESOLVED 9/15/26 = 83'-0". Plan shows two chains 83'-0" and 88'-0" (5'-0" apart, ~2.5 ft at each end = roof overhang). Settled empirically: Parker is built on N-13, N-4 and P-17, all 110 ft deep. At 83'-0" all three clear by ~2 ft; at 88'-0" all three would have been impossible to build. 83'-0" is the body-plus-porch dimension, consistent with the other Heights plans.</t>
         </is>
       </c>
     </row>
@@ -4199,8 +4227,16 @@
       <c r="D53" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="E53" s="48" t="n"/>
-      <c r="F53" s="48" t="n"/>
+      <c r="E53" s="48" t="inlineStr">
+        <is>
+          <t>34'-10"</t>
+        </is>
+      </c>
+      <c r="F53" s="48" t="inlineStr">
+        <is>
+          <t>83'-0"</t>
+        </is>
+      </c>
       <c r="G53" s="48" t="n"/>
       <c r="H53" s="47" t="n">
         <v>1933</v>
@@ -4222,9 +4258,9 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="P53" s="47" t="inlineStr">
-        <is>
-          <t>See note on row 51 — Parker PDF had no usable content. Offered at The Heights only.</t>
+      <c r="P53" s="71" t="inlineStr">
+        <is>
+          <t>See note on row 51 — Parker PDF had no usable content. Offered at The Heights only.  DEPTH RESOLVED 9/15/26 = 83'-0". Plan shows two chains 83'-0" and 88'-0" (5'-0" apart, ~2.5 ft at each end = roof overhang). Settled empirically: Parker is built on N-13, N-4 and P-17, all 110 ft deep. At 83'-0" all three clear by ~2 ft; at 88'-0" all three would have been impossible to build. 83'-0" is the body-plus-porch dimension, consistent with the other Heights plans.</t>
         </is>
       </c>
     </row>
